--- a/docs/dossiers/dossier-paris-11-85bbbf5d.xlsx
+++ b/docs/dossiers/dossier-paris-11-85bbbf5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>63/100</t>
+          <t>60/100</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>Décote sans explication visible dans l'annonce : possible bonne affaire — ou défaut caché (état, copropriété, bail) à vérifier sur place.</t>
+          <t>Décote lisible : des travaux sont signalés dans l'annonce.</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>loyer_estime · rendement_sous_objectif · occupation_a_confirmer</t>
+          <t>loyer_estime · rendement_sous_objectif · surface_a_ventiler · occupation_a_confirmer</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11-85bbbf5d.xlsx
+++ b/docs/dossiers/dossier-paris-11-85bbbf5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11-85bbbf5d.xlsx
+++ b/docs/dossiers/dossier-paris-11-85bbbf5d.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
